--- a/artfynd/A 26039-2023 artfynd.xlsx
+++ b/artfynd/A 26039-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117281401</v>
+        <v>117281399</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:34</t>
+          <t>06:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117281399</v>
+        <v>117281401</v>
       </c>
       <c r="B3" t="n">
-        <v>57789</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -886,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 26039-2023 artfynd.xlsx
+++ b/artfynd/A 26039-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117281399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,8 +920,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117281401</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>